--- a/Excel/12_SupplementaryCO2_WIP_v02.prename.bak.xlsx
+++ b/Excel/12_SupplementaryCO2_WIP_v02.prename.bak.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE9B026F-A196-4BCC-AC40-FAEF48545636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8D3AEE1-32BA-41DF-AF61-192C1182A371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12645" activeTab="4" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15345" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -18,8 +18,11 @@
     <sheet name="Results" sheetId="13" r:id="rId3"/>
     <sheet name="Input - CO2 Use" sheetId="70" r:id="rId4"/>
     <sheet name="12.1.1-2 Supplementary CO2" sheetId="69" r:id="rId5"/>
-    <sheet name="Constants - Common" sheetId="122" r:id="rId6"/>
+    <sheet name="Constants - Common" sheetId="123" r:id="rId6"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId7"/>
+  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -176,6 +179,7 @@
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData_DensityOfMethane_Data">'Constants - Common'!$D$175</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Fertiliser type f","FracGASFf","Basis";"Urea-based fertilisers",0.15,"Urea";"Ammonium-based fertilisers",0.08,"Ammonium";"Nitrate-based fertilisers",0.01,"Nitrate";"Ammonium-nitrate based fertilisers",0.05,"Ammonium-nitrate";"Other fertilisers",0.11,"Other"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_NIRReference">_xlfn.LAMBDA("IPCC 2019 Refinement Volume 4 Table 11.3 [1, p. 11]")</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_Source">_xlfn.LAMBDA("VEERG 2026:Table 12.2.2.9")</definedName>
@@ -1684,116 +1688,6 @@
   <dxfs count="62">
     <dxf>
       <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -2653,6 +2547,116 @@
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3772,6 +3776,26 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -3851,16 +3875,16 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{DC28F2C4-8AF6-4785-8C6B-CEC2944CC2FD}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{BA826D83-A587-4203-B1E6-E5AB7CB217D3}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{294900B6-3C87-45A7-8EDB-09A3701C2F93}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{570F9377-590C-45A2-88C4-0579163D4540}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A05DBB6D-CE50-4268-9475-32BE9CA69194}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{B6A91DC2-A896-483B-990D-C153C84E8114}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3869,16 +3893,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{13B68031-FE71-4BE0-8C8E-1D599536502B}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{9EBE31A5-F469-4D50-8E7E-85256DF3AF70}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{0FC876BB-4FDA-45B1-B871-317669F4973F}" name="Data source">
+    <tableColumn id="1" xr3:uid="{68FB5E3F-4655-4D63-A988-91420A3FE875}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E64587BC-B612-4C18-AC5F-429A1FF42626}" name="Data score">
+    <tableColumn id="2" xr3:uid="{483B6B3C-47D9-40E1-85E8-8561F30444E6}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3887,16 +3911,16 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{54A617B9-FF3E-410C-96A5-4B66BB130A02}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{3FF86950-68CB-42C0-B089-C60D746B8AE3}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{94E6DCBF-2F6C-4DEA-850E-1257E85423A4}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{A4EB55F1-64C2-420C-BAF6-A969104285A6}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C9F029D9-51B8-4816-85D5-3441B1755CA7}" name="FracWET" dataDxfId="30">
+    <tableColumn id="2" xr3:uid="{58C0EB8C-3FFB-42E6-9439-15B18019D100}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3905,7 +3929,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{448ECC07-43ED-47BD-8BF7-B67C65717D36}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{13AFE20E-DAB8-46A4-835D-B77A062973CA}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3914,19 +3938,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{BB4FDCC6-81B1-46EB-A1CB-1E21FDEA30A7}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{FA4BD8BF-4297-4153-A404-E61612B78993}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{CC0A441B-D022-4CA6-8354-A69834BFBFD8}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{19A76A7D-B22B-4F83-A3F3-E659F931F76E}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{40564AE7-BB66-48AF-B3BC-88D951DDE7ED}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{91FC03C9-80F8-4876-B6F3-A091F8B2D2FC}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{3A8B2D33-5F9F-460C-93FA-C0088B196858}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{EFD7456C-3006-41EE-B6B6-0D3EE0D4A261}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{43884D9C-CB71-47BA-ADBF-C46278659C69}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{6DEEEC44-C52E-40C7-AAF4-DD74AA666E25}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3935,16 +3959,16 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{4D75122A-64DD-44AC-906A-4556B88FCA94}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{9E829E9F-C966-439A-B9BA-B3116C8C82B5}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{814E6C27-AEC4-4F58-94DF-EB6BF6F8DEE2}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{A150E63D-D5D5-420D-9154-9DFE21F76D8B}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B95AAA77-7FB1-4F2D-8530-6B063DBAAC65}" name="FracWET" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{960A6E10-919B-40F0-9AAC-80B19FA883DF}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3953,16 +3977,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{A48CC38B-BA4A-461A-8A4A-F73E8E890799}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{7F95BE01-A12C-4A48-AAE9-836A6A257618}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{22812ECF-2BDF-479B-BDD0-ABDD9D181FA2}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{73312A31-9282-435C-B4FD-1741806CF3D5}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F6379345-454B-47D5-B6BF-10AC3FD1C963}" name="EFPRP" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{2398AAE0-CBD9-4CC5-9261-199C4BABBBFC}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3971,16 +3995,16 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{2013A3BB-DB3F-4651-BAF5-B2BC62FF8643}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{26DE116F-1367-457C-9404-2B393E2C7199}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{39B089BF-12E1-4543-87BC-10C6A0C6FFD9}" name="Month">
+    <tableColumn id="1" xr3:uid="{C1B98E3B-FA94-489F-BD3B-C07B2E339C6A}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1F8FDC7C-6656-4185-B6E7-8E523E08EB97}" name="Season" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{AF160977-285F-461C-87EC-A6DF21119737}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3989,7 +4013,7 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{CB579B7F-3F35-4411-A973-C63A8EB50780}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{EB3EC85D-9E46-461E-9649-64C43AF24597}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4009,52 +4033,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{6ADC392C-5850-4DF1-B61E-AD89C6F0C73A}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{65759346-796F-43D7-8366-FEA179A14364}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{BB6F7FCE-22AE-4D28-A913-77E6DA4EEDBA}" name="MAT (ºC)" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{631A43E6-41BE-47E5-94C7-FA342E1A327D}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{13CC30B5-CFBC-4FBD-A997-7404CA96F1DC}" name="Anaerobic lagoon" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{4EF04B9F-2FFC-4301-9B96-15CE61973FFB}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8377B2BA-D9A3-4F3B-9CDA-463B9C7C6D0B}" name="Digester / covered lagoons" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{2E532650-CFFA-406F-A906-F961444D0125}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{8F8FE17C-A26D-4015-8DE7-8A0284CCF305}" name="Liquid systems" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{4CEAE059-39A1-469F-B121-D4C01CC98BEB}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{335544B6-26CF-4063-8B41-14ACFA814834}" name="Daily spread" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{634C88DA-789E-4F3E-AD75-0D9B2CC22D7A}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{ED337F61-FBEF-437D-B2EA-429DF88BF98B}" name="Composting (passive windrow)" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{7CB045DF-8515-472B-8158-83166437C71E}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{7A316A78-DAB2-4C8A-BD7A-5BAB30008B7C}" name="Solid storage" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{7F3E3A55-68A1-4AA9-9F23-C61AE74A2514}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{ED235F5C-8782-4085-ACE9-5581BEFF0447}" name="Pit storage" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{B82E9EB0-5535-44D4-9618-1AAA7BDC367B}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{82BDA5BE-621D-463B-8C21-FE2122E0D19D}" name="Deep litter" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{2529BF8F-25D0-4850-9EE6-23E95AA4CA15}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{A89BA2F9-19A1-47F2-B204-07445F32B7EA}" name="Poultry manure with bedding" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{42CCE495-EA11-4EBD-AFD3-DCB807AA5093}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{5843EC54-CAD6-4A10-8170-CA7C4C5ED5F5}" name="Poultry manure without bedding" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{33C823A7-DDEF-4B47-B312-ABC9EE05E434}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{8DE32C71-B502-409B-928F-750CCA16648F}" name="Direct processing" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{1BEA7237-0720-46D5-A66F-0710B3A5BFBC}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{27CA3685-3894-4D69-B24B-CA075337B41C}" name="Direct application" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{69E72303-413D-42E5-894E-6A4D2D34DC21}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{99559C44-EEE8-4D8F-A9A8-FCC203F32BB3}" name="Pasture range and paddock" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{97061746-B7EA-454C-BA50-4B42EFB3F0E0}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{66B87B0B-81DA-4A7A-9AF4-43E1B0D7455E}" name="MAT raw" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{E3E26496-FF78-4D80-83DE-52E9EB25004A}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4063,16 +4087,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{0E617B26-18D0-4AFA-82FE-00AED0900410}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{2E287AB9-D857-42CA-9329-53B9F1A93764}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{DB5A1BF0-2654-4654-A005-25B68250353F}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{F2B97538-2A93-4A5F-821B-63333CB37CB8}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DC92C861-4FEA-4BB5-A89C-E12CFC7C9D9E}" name="EFNi &amp; EFN2Oi" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{D0D4FB0D-6804-45B0-A258-9C18A5FBEF67}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4081,20 +4105,20 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BFEFA86D-B928-4343-A1C3-8AACEDBA85DF}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9AADC772-EA5E-433B-91D5-0C82352E20A5}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8DC65857-1762-4DED-831A-06826FC8E599}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{9475A86E-019F-4C77-B082-710B26588B4B}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{FE185B29-9557-4581-BF86-603C43AB533D}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{0E6BB605-9345-49CD-98CE-B1FF7E9E599C}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{2A95011F-50D1-4289-9E7F-3DF967FE98BA}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{AAE59A34-4695-4ED0-896B-485989902F58}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4103,12 +4127,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4A19D36B-5E63-4974-A793-136379A355A9}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{18E938AA-6F08-4062-B88A-24FC0304890A}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{9C5723D8-D0B4-4125-9BBC-4DDD424173F8}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{8B1C097D-25DC-42D1-8D9B-E0AE1E3C5625}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4117,16 +4141,16 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{94DE9EAB-5015-4060-9BC2-2CD8F0DDFF50}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{79D12EAB-B378-41DF-8647-DA9306E8B228}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4001CBA9-F4A3-4C7D-A275-B1BA3E362739}" name="Gas">
+    <tableColumn id="1" xr3:uid="{065C13CF-96F2-4C01-8AFC-EE5E672E3445}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3AD90266-42FF-4CC8-A75A-9C805610DB6E}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{F297B39A-0108-4B97-BE42-3842A5BC196A}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4135,7 +4159,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{C444C88D-010B-4CAA-8EC7-6D34E52C3F4A}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2F69636A-061F-4F7D-89A6-5D0C403191BE}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4144,19 +4168,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{3A8C0CFA-3DE9-498C-966D-6B244E120A7E}" name="Gas">
+    <tableColumn id="1" xr3:uid="{75DB43C9-F9A1-4150-8FDB-431E493449DF}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{92DAC899-6F8B-4D13-8C45-81CFF6F286F1}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{87D9FA60-95A8-455D-8335-282ED727679E}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{28F8688B-CF96-482A-8C40-083526955682}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{D5861B41-6E53-4E00-86C1-8543D2408553}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8770A909-8C13-47E9-AD96-8C67877643DF}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{DCD51FCF-1F4B-4487-9A72-0A768B15987C}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D670556D-4DF6-4786-BA8A-09C654C17DB9}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{087CA5C0-6ADC-4106-A054-BCDF5C169AC6}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4165,7 +4189,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{781EDDAF-7F9B-48B0-A342-31E9122F53DD}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{E2AA9DA4-746B-4D65-9342-E8D154658AC9}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4185,52 +4209,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{8D40750F-7330-456A-BB21-E3EFB286833F}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{997233F6-DEF8-4C23-B971-48F0B211B5E1}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{62E66C4A-4479-4A17-B98A-2F53B0DF4466}" name="MAT" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{6C078087-8413-48FD-9ABC-A81F79A0365F}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B9FC8F4B-35F5-4F7B-8E1C-CE583C7FC041}" name="MAP" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{E06E46AB-F2A3-4D0E-9DA8-6019416CB348}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{380F7CFF-6056-41A6-BF80-BBCCEE00662F}" name="Frost days per year" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{61B5387C-8E7E-4348-B844-0DD6EDB18152}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{02CC8E12-B022-4DEC-B7E6-726532DF5644}" name="Elevation" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{5D2D1E36-05BB-4AF5-A109-2E81B7E0E27E}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{115D7C7A-B275-48F4-8B1D-23731CD5E9FD}" name="MAP:PET" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{9CEAA2A2-E598-4FB9-878C-67089701E719}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{4116C12D-F410-4E10-93F9-6434C598BA9E}" name="Min temp" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{75BEB992-6841-4944-B52E-149C1BAC548A}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{540A3023-64D8-4CEB-8D95-A6D179AA549E}" name="Max temp" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{A96FE33C-AA42-4EFA-A6FE-656C06685D13}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{D64547E2-0462-4E06-854A-CCF17A6318D7}" name="Min rainfall" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{5E853EA5-0EA6-4591-9BFC-AF5B0D66899D}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{655EDD60-857F-42AC-A2BF-DEC3DFB090B0}" name="Max rainfall" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{34EB25A8-147A-4AA4-BAB6-7861FC26CF59}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{7278EB04-7DA4-4E3B-919C-4FEB67D4C659}" name="Min frost days" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{C73E5785-0912-4BDE-A383-519AAB857EB8}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{BE43C499-B1F6-40CB-823D-961D21AEEAA3}" name="Max frost days" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{B343787C-D2A5-44ED-81A8-C9D48FC86826}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{D03997E9-53F2-4697-B878-CFFFC9520B10}" name="Min elevation" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{211ACD6B-7B0C-4CD1-B7A3-746D95F86A1C}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{C44A8FA0-40DC-4D7B-94F7-F219584A1AD7}" name="Max elevation" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{E0B8BDED-4D50-4C16-8DC2-2E8CBA07045A}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{A2246660-C845-4D9C-9366-7ECECC01DF7C}" name="Min MAP:PET" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{D9925134-ABBF-4B7B-B0CA-BF1D5863F478}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{AB61D1E6-3618-40D8-826C-ABEBBE7DF2B0}" name="Max MAP:PET" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{F8AF9ED0-1B38-41E1-8A6B-CF841FB00275}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4239,16 +4263,16 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{57EBC0E9-F0EE-409B-B02B-65F95E0DBD10}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{053938B7-C961-4EBE-8CA7-CD0617572E79}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{30DD4BB3-ABE2-4C86-A881-C32DBDC5DA0E}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{A45ADA6E-9BDC-47FA-B55B-CCC0AFF4AE82}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D6850548-4D06-4192-95CD-9B52C1BD5D14}" name="Wet or Dry Zone" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{181513E9-A040-49E4-98DD-73697CAD90FF}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4257,7 +4281,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{4DCD1AF7-0F5B-4776-A34C-5F60347B0D68}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{6E5DC716-352E-494D-84FE-89EC306148F6}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4265,16 +4289,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{AA691C71-D51E-4A4F-8321-B70D5A2166C7}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{A1644AD4-DEA1-4785-AEB8-89154E24F05C}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5E81B5F6-3184-4C46-B272-8A55D7855886}" name="MAT">
+    <tableColumn id="2" xr3:uid="{893DC201-1D6E-4DCB-B67B-9B3D5605FEF2}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B59D4E84-94D9-4E61-A29D-6B62F741B5BA}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{41E5D688-8D27-4F0A-A5DA-172049ABD36B}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BBD14DC8-B942-4A1D-9E63-811222BB9D53}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{FAD8E530-E470-49D6-86B2-C27C2F7293AE}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4283,7 +4307,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{E977CA12-7C95-4E57-894A-0768785E4B72}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{49DB768F-E4DE-437B-A85D-D4CA096DA3EC}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4291,16 +4315,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{5140A975-6A60-4280-BCE4-6B97A4BAA3EC}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{6617EBEB-D565-4DAC-A5B9-A1337C720E0E}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{ABCF8B7A-FBDB-4E6C-BEA6-908DC8354C80}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{0B52BDC6-B9A6-457D-89D5-C9813110D291}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{64A764CC-9EBF-4E70-88E8-EA1D64C310D4}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{97EEB659-9CC4-4892-AE7F-3B354DDDC201}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{94CC1A4B-3582-43CC-86D9-A0C469CEAF18}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{99B62BD1-9354-4A0B-8AF0-87E39BB6F9F2}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5880,57 +5904,57 @@
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="F47 E200 F210">
-    <cfRule type="cellIs" dxfId="10" priority="62" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="62" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F126:F127">
-    <cfRule type="cellIs" dxfId="9" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F138:F139">
-    <cfRule type="cellIs" dxfId="8" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F150:F151">
-    <cfRule type="cellIs" dxfId="7" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F162:F163">
-    <cfRule type="cellIs" dxfId="6" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F250:F251">
-    <cfRule type="cellIs" dxfId="5" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F255:F256">
-    <cfRule type="cellIs" dxfId="4" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F260:F261">
-    <cfRule type="cellIs" dxfId="3" priority="91" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="91" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F284:F285">
-    <cfRule type="cellIs" dxfId="2" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F289:F290">
-    <cfRule type="cellIs" dxfId="1" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F294:F295">
-    <cfRule type="cellIs" dxfId="0" priority="83" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="83" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6438,7 +6462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BDDFF2-3D95-47BA-886B-648B3235344C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC5BC484-BB6E-45FA-82B3-176CB9E1966E}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -10430,19 +10454,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADIALgAxADoAIABTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMgAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAdQBzAGUAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AUQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4AUQAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAIAB1AHMAZQBkACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAG8AcABlAHIAYQB0AGkAbwBuAHMAIAAoAGsAZwAgAEMATwAyACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEALABcAG4AIAAgACAAIABRACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAdQBzAGUAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADIALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBRAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAIAB1AHMAZQBkACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAawBnACAAQwBPADIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVABpAHQAbABlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBVAG4AaQB0ACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFMAbwB1AHIAYwBlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -10637,34 +10659,31 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMgAuADEAOgAgAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAyAC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBcAG4ARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4ARQBcAG4AdAAgAEMATwAyAGUAXABuAEUAPQBRAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgAgAHUAcwBlAGQAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgACgAawBnACAAQwBPADIAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQAsAFwAbgAgACAAIAAgAFEAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMgAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFEAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgAgAHUAcwBlAGQAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAbwBwAGUAcgBhAHQAaQBvAG4AcwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBUAGkAdABsAGUAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFUAbgBpAHQAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AUwBvAHUAcgBjAGUAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10683,13 +10702,18 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Excel/12_SupplementaryCO2_WIP_v02.prename.bak.xlsx
+++ b/Excel/12_SupplementaryCO2_WIP_v02.prename.bak.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8D3AEE1-32BA-41DF-AF61-192C1182A371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFDF0943-8D47-40C7-84A5-45F0A0EA0790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15345" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="28800" windowHeight="15345" firstSheet="5" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Results" sheetId="13" r:id="rId3"/>
     <sheet name="Input - CO2 Use" sheetId="70" r:id="rId4"/>
     <sheet name="12.1.1-2 Supplementary CO2" sheetId="69" r:id="rId5"/>
-    <sheet name="Constants - Common" sheetId="123" r:id="rId6"/>
+    <sheet name="Constants - Common" sheetId="124" r:id="rId6"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId7"/>
@@ -38,7 +38,17 @@
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Title">_xlfn.LAMBDA("Convert nitrous oxide emissions to carbon dioxide equivalent emissions")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Variable">_xlfn.LAMBDA("EN2O CO2e")</definedName>
-    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
+    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray,
+    _xlfn.XLOOKUP(
+        MEDIAN(
+            ROUND(_xlpm.Temperature, 0),
+            MIN(_xlpm.TemperatureArray),
+            MAX(_xlpm.TemperatureArray)
+        ),
+        _xlpm.TemperatureArray,
+        _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)
+    )
+)</definedName>
     <definedName name="Common_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingPeriods">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag))))</definedName>
@@ -54,9 +64,28 @@
     <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTable">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIfFalse,
+    IFERROR(
+        _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1,
+            _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)
+        ),
+        IF(_xlfn.ISOMITTED(_xlpm.ValueIfFalse), "", _xlpm.ValueIfFalse)
+    )
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIFFalse,
+    _xlfn.XLOOKUP(1, (_xlpm.LookupArray1=_xlpm.LookupValue1)*(_xlpm.LookupArray2=_xlpm.LookupValue2), _xlpm.ReturnArray, IF(_xlfn.ISOMITTED(_xlpm.ValueIFFalse), "", _xlpm.ValueIFFalse))
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell,
+    SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) -1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlink">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet">_xlfn.LAMBDA(_xlpm.TargetCell,
+  _xlfn.LET(
+    _xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"),
+    _xlpm.addr, CELL("address", _xlpm.TargetCell),
+    "#" &amp; _xlpm.addr
+  )
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
     <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -3875,16 +3904,16 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{BA826D83-A587-4203-B1E6-E5AB7CB217D3}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{84B33235-C1AD-4A32-A81A-A9863F23D804}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{570F9377-590C-45A2-88C4-0579163D4540}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{3AA52A1F-70D6-4171-A77E-955CDC2AAF44}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B6A91DC2-A896-483B-990D-C153C84E8114}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{84D2C837-6A19-4918-A9E4-B27F208D21AE}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3893,16 +3922,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{9EBE31A5-F469-4D50-8E7E-85256DF3AF70}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{621E877A-FD87-4E93-9BBF-B6E4BE9A327D}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{68FB5E3F-4655-4D63-A988-91420A3FE875}" name="Data source">
+    <tableColumn id="1" xr3:uid="{F591A62B-F42B-47A3-94D3-A550761E6E4E}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{483B6B3C-47D9-40E1-85E8-8561F30444E6}" name="Data score">
+    <tableColumn id="2" xr3:uid="{FFEF2FD6-C2F4-43F6-9983-4E88555032FE}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3911,16 +3940,16 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{3FF86950-68CB-42C0-B089-C60D746B8AE3}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{8054B9FA-2E64-458C-BBB7-127F8F5CF09D}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A4EB55F1-64C2-420C-BAF6-A969104285A6}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{21D27BB0-97FE-4314-A606-2631BFF08EDF}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{58C0EB8C-3FFB-42E6-9439-15B18019D100}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{84F263C8-B14B-4647-80BD-D0C4BF09AFFE}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3929,7 +3958,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{13AFE20E-DAB8-46A4-835D-B77A062973CA}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{29C3416F-C1C0-4BD0-8423-7BB19735139A}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3938,19 +3967,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{FA4BD8BF-4297-4153-A404-E61612B78993}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{81E1F936-9300-4941-BAB7-495795E69DF4}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{19A76A7D-B22B-4F83-A3F3-E659F931F76E}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{8ADC40CE-6F4B-4863-9F9F-F408F66F8BBB}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{91FC03C9-80F8-4876-B6F3-A091F8B2D2FC}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{95A0C90C-F9BE-4948-A561-19F6BE3FE2AD}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EFD7456C-3006-41EE-B6B6-0D3EE0D4A261}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{D7EB0160-CF6F-4466-B61A-BEC17026B874}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6DEEEC44-C52E-40C7-AAF4-DD74AA666E25}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{9667CE50-6947-4D70-8CDC-D887AF66EF74}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3959,16 +3988,16 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{9E829E9F-C966-439A-B9BA-B3116C8C82B5}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{D947605A-0ABC-43BE-8C7D-491BDF7C27EA}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A150E63D-D5D5-420D-9154-9DFE21F76D8B}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{7253E0BD-4B9C-4082-8CD0-533878135E2D}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{960A6E10-919B-40F0-9AAC-80B19FA883DF}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{8A49E796-F440-4486-9D31-310C48C19AA8}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3977,16 +4006,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{7F95BE01-A12C-4A48-AAE9-836A6A257618}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{33032657-036B-4399-B537-A715FE6CF5A5}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{73312A31-9282-435C-B4FD-1741806CF3D5}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{F50D9CD9-8150-4FF7-8496-B2A382583C48}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2398AAE0-CBD9-4CC5-9261-199C4BABBBFC}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{496B48CC-445F-4DBE-BC28-1C50B65CECDF}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3995,16 +4024,16 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{26DE116F-1367-457C-9404-2B393E2C7199}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{B584E57E-AF85-49E8-8F48-B69DA2E00DF7}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{C1B98E3B-FA94-489F-BD3B-C07B2E339C6A}" name="Month">
+    <tableColumn id="1" xr3:uid="{4CEE1CD7-E0B9-48F8-8C52-24A697C0AC64}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AF160977-285F-461C-87EC-A6DF21119737}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{E2095DD8-B7A1-458B-8C5A-1243300AF666}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4013,7 +4042,7 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{EB3EC85D-9E46-461E-9649-64C43AF24597}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{6F93DA02-717C-477A-9FEC-C34313715E74}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4033,52 +4062,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{65759346-796F-43D7-8366-FEA179A14364}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{562389D9-E360-4D90-9166-8E5404B3D899}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{631A43E6-41BE-47E5-94C7-FA342E1A327D}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{9F4008C0-51F5-474E-BF7F-EE05F1CB3E81}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{4EF04B9F-2FFC-4301-9B96-15CE61973FFB}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{DF83C2CB-5BE9-4DAC-878C-AB21F8F31EC9}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{2E532650-CFFA-406F-A906-F961444D0125}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{7B71FBEC-0D74-48B7-90C0-E62287A3D839}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{4CEAE059-39A1-469F-B121-D4C01CC98BEB}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{29EBED53-2DCB-455B-95B0-2E559EA3ED6F}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{634C88DA-789E-4F3E-AD75-0D9B2CC22D7A}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{D94A6971-80BE-4D20-B977-15A555D7797B}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{7CB045DF-8515-472B-8158-83166437C71E}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{122D4850-E150-472C-953C-18D2332647BD}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{7F3E3A55-68A1-4AA9-9F23-C61AE74A2514}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{ED0AABC6-0226-470B-B1F9-9983E0408E60}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{B82E9EB0-5535-44D4-9618-1AAA7BDC367B}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{831E963A-A3FD-4960-8C62-073BE18644AF}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{2529BF8F-25D0-4850-9EE6-23E95AA4CA15}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{DFC0062A-7B0A-4514-9890-3F311036B76D}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{42CCE495-EA11-4EBD-AFD3-DCB807AA5093}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{0AA75820-4A89-4FB8-B12C-7EEFFA929FD2}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{33C823A7-DDEF-4B47-B312-ABC9EE05E434}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{A763C1C4-C78D-4637-A6B9-FADEA4295287}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{1BEA7237-0720-46D5-A66F-0710B3A5BFBC}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{1D52D216-7E68-4A77-8F2C-E22F833B3C40}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{69E72303-413D-42E5-894E-6A4D2D34DC21}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{D9DE22B7-9262-45F8-81C1-978ABD8273BE}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{97061746-B7EA-454C-BA50-4B42EFB3F0E0}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{A161A62C-6149-46FE-A048-32EB9A77334C}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{E3E26496-FF78-4D80-83DE-52E9EB25004A}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{A7DF95CD-B80F-48C3-9D47-3C7716BAED56}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4087,16 +4116,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{2E287AB9-D857-42CA-9329-53B9F1A93764}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{CBD4E2A9-7FAA-4EED-9B12-7A1ABBC7E12F}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F2B97538-2A93-4A5F-821B-63333CB37CB8}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{4AD14D9B-5D6C-4C82-B0FC-265FB1FDE94F}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D0D4FB0D-6804-45B0-A258-9C18A5FBEF67}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{972114D3-F127-48F6-88EA-5F002105484D}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4105,20 +4134,20 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9AADC772-EA5E-433B-91D5-0C82352E20A5}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{27B87109-C748-4433-8E6B-150AACBD95A3}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{9475A86E-019F-4C77-B082-710B26588B4B}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{D38F7A74-BF74-4D74-82CC-35F768F2F093}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0E6BB605-9345-49CD-98CE-B1FF7E9E599C}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{00705D98-E706-4742-BD1F-753673D3F8AA}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{AAE59A34-4695-4ED0-896B-485989902F58}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{A4EC0458-E116-430D-9B0E-9EB2CF9A1CEE}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4127,12 +4156,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{18E938AA-6F08-4062-B88A-24FC0304890A}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{98184834-8BFC-4957-A6FD-0C2F268108E3}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{8B1C097D-25DC-42D1-8D9B-E0AE1E3C5625}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{B5424F4F-5770-4242-AC1A-D079085B52AC}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4141,16 +4170,16 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{79D12EAB-B378-41DF-8647-DA9306E8B228}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{E42504E2-9A68-4869-8034-7AD810F23E06}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{065C13CF-96F2-4C01-8AFC-EE5E672E3445}" name="Gas">
+    <tableColumn id="1" xr3:uid="{AA835B6E-52DB-4301-B6A4-65BD375FF6EA}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F297B39A-0108-4B97-BE42-3842A5BC196A}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{ECDBE1A2-F3E2-436F-8F5B-D081C71CACC9}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4159,7 +4188,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2F69636A-061F-4F7D-89A6-5D0C403191BE}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{F60E1594-AD68-42BC-9D58-2F910411ECED}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4168,19 +4197,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{75DB43C9-F9A1-4150-8FDB-431E493449DF}" name="Gas">
+    <tableColumn id="1" xr3:uid="{A8C6E91C-2867-472F-82D3-ED62BB5F274F}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{87D9FA60-95A8-455D-8335-282ED727679E}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{BCC633BD-A394-4B1E-B739-509F6F18BAAB}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D5861B41-6E53-4E00-86C1-8543D2408553}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{BD43293F-3FCC-4273-83B8-51F9CBB5FE31}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DCD51FCF-1F4B-4487-9A72-0A768B15987C}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{E1D00FD7-22AC-489E-8F9D-22FCDE475EDF}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{087CA5C0-6ADC-4106-A054-BCDF5C169AC6}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{2FEC2588-E4D2-4BF3-A15C-664F97D98112}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4189,7 +4218,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{E2AA9DA4-746B-4D65-9342-E8D154658AC9}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{E175515F-FA22-4209-8ACB-E08DCC681D6D}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4209,52 +4238,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{997233F6-DEF8-4C23-B971-48F0B211B5E1}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{350201D1-0C40-4559-9C6A-CE6ABAB0E1CA}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6C078087-8413-48FD-9ABC-A81F79A0365F}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{58C3259C-8259-44AA-8F7D-60BD3BA31CFB}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{E06E46AB-F2A3-4D0E-9DA8-6019416CB348}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{D937B589-0413-4817-8E6F-FB4F0093B712}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{61B5387C-8E7E-4348-B844-0DD6EDB18152}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{15517AC5-09C7-4317-9BFA-3EF34E65F6F8}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{5D2D1E36-05BB-4AF5-A109-2E81B7E0E27E}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{C2A39B92-0D2C-47FE-BB93-BA4E95CEB839}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{9CEAA2A2-E598-4FB9-878C-67089701E719}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{685978F7-F458-4A32-A566-1BCB374A0116}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{75BEB992-6841-4944-B52E-149C1BAC548A}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{F78C08A7-755F-4398-BA75-45258C33CAF9}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{A96FE33C-AA42-4EFA-A6FE-656C06685D13}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{CF3A75D9-2A19-4503-942A-A1E0A6581549}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{5E853EA5-0EA6-4591-9BFC-AF5B0D66899D}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{FFC784E5-E1F1-4E57-8211-CAB88317F6A9}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{34EB25A8-147A-4AA4-BAB6-7861FC26CF59}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{6E155625-963F-4EC9-B7F6-867A29918389}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{C73E5785-0912-4BDE-A383-519AAB857EB8}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{B80F5E14-C6DA-4F8C-AB70-46C6E4CC2AAB}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{B343787C-D2A5-44ED-81A8-C9D48FC86826}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{9F5C3AA6-7016-4A59-8AA1-562A1CA9F792}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{211ACD6B-7B0C-4CD1-B7A3-746D95F86A1C}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{C280D45A-401E-4E85-BC00-EF52B6D37151}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{E0B8BDED-4D50-4C16-8DC2-2E8CBA07045A}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{00CBF46E-B3D2-43B0-B68D-820CCB35C667}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{D9925134-ABBF-4B7B-B0CA-BF1D5863F478}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{E87174CE-6F99-49AD-8DD2-4B07838D93A4}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{F8AF9ED0-1B38-41E1-8A6B-CF841FB00275}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{B751773D-2096-4AC6-B881-8B6A6F9668F1}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4263,16 +4292,16 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{053938B7-C961-4EBE-8CA7-CD0617572E79}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{DF4E6C8A-FB7E-4D62-9AEF-AC775E1600D5}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A45ADA6E-9BDC-47FA-B55B-CCC0AFF4AE82}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{AB0599FB-6465-4F23-ADB6-CC07426C5824}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{181513E9-A040-49E4-98DD-73697CAD90FF}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{A61DAD2E-0426-460F-9676-B14B545ACB5A}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4281,7 +4310,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{6E5DC716-352E-494D-84FE-89EC306148F6}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{247A4E54-7567-4B71-B8D9-24D5CC56BE9A}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4289,16 +4318,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A1644AD4-DEA1-4785-AEB8-89154E24F05C}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{2A007C11-A800-4071-8AFB-955E2EE22006}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{893DC201-1D6E-4DCB-B67B-9B3D5605FEF2}" name="MAT">
+    <tableColumn id="2" xr3:uid="{6A2F6ED6-06A5-4EBD-BEBD-03E744FF35D8}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{41E5D688-8D27-4F0A-A5DA-172049ABD36B}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{D6067325-BA7C-4E56-9443-7E5413F4CA36}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{FAD8E530-E470-49D6-86B2-C27C2F7293AE}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{F30E353F-0351-4B0D-BAD5-309FCB0D3A11}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4307,7 +4336,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{49DB768F-E4DE-437B-A85D-D4CA096DA3EC}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{C9BB04FC-37AA-4F6B-BD47-89B8576C9126}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4315,16 +4344,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{6617EBEB-D565-4DAC-A5B9-A1337C720E0E}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{3217A6B7-106A-417E-B60B-E90F0FB0873B}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0B52BDC6-B9A6-457D-89D5-C9813110D291}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{5631EC92-48F0-4C46-830B-1CEEBF561144}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{97EEB659-9CC4-4892-AE7F-3B354DDDC201}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{5D0E8120-8D2F-40DF-8056-3A0D7F76103F}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{99B62BD1-9354-4A0B-8AF0-87E39BB6F9F2}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{A98E480B-626D-4439-9897-2EF6A669DFB9}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6462,7 +6491,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC5BC484-BB6E-45FA-82B3-176CB9E1966E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{373C789C-70AA-4551-B1E7-DAA15A2C37E8}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -10454,6 +10483,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMgAuADEAOgAgAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAyAC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBcAG4ARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4ARQBcAG4AdAAgAEMATwAyAGUAXABuAEUAPQBRAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgAgAHUAcwBlAGQAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgACgAawBnACAAQwBPADIAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQAsAFwAbgAgACAAIAAgAFEAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMgAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFEAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgAgAHUAcwBlAGQAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAbwBwAGUAcgBhAHQAaQBvAG4AcwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBUAGkAdABsAGUAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFUAbgBpAHQAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AUwBvAHUAcgBjAGUAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -10464,7 +10497,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -10659,7 +10692,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -10668,11 +10701,15 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMgAuADEAOgAgAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAyAC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBcAG4ARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4ARQBcAG4AdAAgAEMATwAyAGUAXABuAEUAPQBRAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgAgAHUAcwBlAGQAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgACgAawBnACAAQwBPADIAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQAsAFwAbgAgACAAIAAgAFEAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMgAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFEAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgAgAHUAcwBlAGQAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAbwBwAGUAcgBhAHQAaQBvAG4AcwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBUAGkAdABsAGUAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFUAbgBpAHQAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AUwBvAHUAcgBjAGUAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -10683,7 +10720,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10702,18 +10739,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>